--- a/analysis/paper tables and figures/figure 4 module completions.xlsx
+++ b/analysis/paper tables and figures/figure 4 module completions.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\misc\GitHub\FuzzDojo\analysis\paper tables and figures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SW\Desktop\1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12460" tabRatio="500"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="23263" windowHeight="12463" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Demographics" sheetId="14" r:id="rId1"/>
@@ -666,7 +666,7 @@
                   <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>17</c:v>
@@ -717,8 +717,8 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="100"/>
-        <c:axId val="536250536"/>
-        <c:axId val="536250144"/>
+        <c:axId val="663285344"/>
+        <c:axId val="663284560"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -895,11 +895,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="536250536"/>
-        <c:axId val="536250144"/>
+        <c:axId val="663285344"/>
+        <c:axId val="663284560"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="536250536"/>
+        <c:axId val="663285344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1010,7 +1010,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="536250144"/>
+        <c:crossAx val="663284560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1018,7 +1018,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="536250144"/>
+        <c:axId val="663284560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1125,7 +1125,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="536250536"/>
+        <c:crossAx val="663285344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2076,12 +2076,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="9.90625" customWidth="1"/>
+    <col min="1" max="1" width="12.4609375" customWidth="1"/>
+    <col min="4" max="4" width="9.921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2098,7 +2099,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -2115,7 +2116,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2132,7 +2133,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2149,7 +2150,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -2166,7 +2167,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -2183,7 +2184,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -2200,7 +2201,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2214,10 +2215,10 @@
         <v>16</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2234,7 +2235,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -2251,7 +2252,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2268,7 +2269,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -2285,7 +2286,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -2302,7 +2303,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -2319,7 +2320,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -2336,7 +2337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2353,7 +2354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2370,7 +2371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -2387,7 +2388,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -2398,7 +2399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>2</v>
       </c>
@@ -2412,7 +2413,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>0</v>
       </c>
